--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487778_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487778_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.253</v>
+        <v>6.8168</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3802</v>
+        <v>6.2964</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8728</v>
+        <v>0.5204</v>
       </c>
       <c r="G2" t="n">
         <v>2.4995</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4829</v>
+        <v>1.0468</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7358</v>
+        <v>0.652</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7471</v>
+        <v>0.3948</v>
       </c>
       <c r="V2" t="n">
         <v>1.3975</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>J. JERMAIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1438</v>
+        <v>2.602</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4285</v>
+        <v>2.1727</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7153</v>
+        <v>0.4294</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6475</v>
+        <v>-0.6979</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0875</v>
+        <v>0.4198</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4401</v>
+        <v>-1.1177</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1451</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2627</v>
+        <v>1.4407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1176</v>
+        <v>-0.6932</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5023</v>
+        <v>-1.4454</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8248</v>
+        <v>-1.0209</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3225</v>
+        <v>-0.4245</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.7461</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.3705</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7861</v>
+        <v>1.2999</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1928</v>
+        <v>1.0683</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5933</v>
+        <v>0.2317</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7513</v>
+        <v>1.1675</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7513</v>
+        <v>1.3975</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. JERMAIN</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6003</v>
+        <v>1.8814</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4645</v>
+        <v>0.8248</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1358</v>
+        <v>1.0566</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6979</v>
+        <v>1.146</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4198</v>
+        <v>1.3582</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1177</v>
+        <v>-0.2123</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.9786</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4407</v>
+        <v>0.9786</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6932</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4454</v>
+        <v>0.1674</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0209</v>
+        <v>0.3796</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4245</v>
+        <v>-0.2123</v>
       </c>
       <c r="P4" t="n">
         <v>0.8325</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2981</v>
+        <v>-0.097</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3601</v>
+        <v>-0.1538</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0619</v>
+        <v>0.0568</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5467</v>
+        <v>1.5788</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1844</v>
+        <v>0.0533</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7311</v>
+        <v>1.5255</v>
       </c>
       <c r="G5" t="n">
         <v>0.7985</v>
@@ -844,13 +844,13 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0437</v>
+        <v>-0.0116</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4567</v>
+        <v>-0.2191</v>
       </c>
       <c r="U5" t="n">
-        <v>0.413</v>
+        <v>0.2075</v>
       </c>
       <c r="V5" t="n">
         <v>0.5838</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5035</v>
+        <v>-0.4244</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6524</v>
+        <v>-1.4351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8511</v>
+        <v>1.0106</v>
       </c>
       <c r="G6" t="n">
-        <v>1.146</v>
+        <v>-0.6475</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3582</v>
+        <v>-1.0875</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2123</v>
+        <v>0.4401</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9786</v>
+        <v>-0.1451</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9786</v>
+        <v>-0.2627</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1176</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1674</v>
+        <v>-0.5023</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3796</v>
+        <v>-0.8248</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2123</v>
+        <v>0.3225</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>-3.7461</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.3705</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.475</v>
+        <v>2.2179</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3262</v>
+        <v>1.3292</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1487</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6820000000000001</v>
+        <v>-0.7272</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1748</v>
+        <v>-0.2098</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4928</v>
+        <v>-0.5174</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.0265</v>
+        <v>-1.2848</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2476</v>
+        <v>-0.9827</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7789</v>
+        <v>-0.3021</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7074</v>
+        <v>-0.0232</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6021</v>
+        <v>-0.6804</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1053</v>
+        <v>0.6572</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.319</v>
+        <v>-1.2616</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6455</v>
+        <v>-0.3023</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6735</v>
+        <v>-0.9593</v>
       </c>
       <c r="P7" t="n">
         <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9998</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>3.671</v>
+        <v>0.8539</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3289</v>
+        <v>0.1012</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7076</v>
+        <v>-0.8137</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6321</v>
+        <v>-0.7911</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7037</v>
+        <v>0.5255</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9284</v>
+        <v>-1.3166</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2848</v>
+        <v>-3.0265</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9827</v>
+        <v>-2.2476</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3021</v>
+        <v>-0.7789</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0232</v>
+        <v>-0.7074</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6804</v>
+        <v>-0.6021</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6572</v>
+        <v>-0.1053</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2616</v>
+        <v>-2.319</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3023</v>
+        <v>-1.6455</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9593</v>
+        <v>-0.6735</v>
       </c>
       <c r="P8" t="n">
         <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0502</v>
+        <v>2.5267</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3601</v>
+        <v>2.0217</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3099</v>
+        <v>0.505</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8137</v>
+        <v>-0.7076</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8137</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9259</v>
+        <v>-1.188</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.338</v>
+        <v>0.3654</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4122</v>
+        <v>-1.5534</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3762</v>
+        <v>-1.6255</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5051</v>
+        <v>-0.8401</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8711</v>
+        <v>-0.7854</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.629</v>
+        <v>0.8364</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1727</v>
+        <v>0.5196</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8017</v>
+        <v>0.3167</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7472</v>
+        <v>-2.4619</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6778</v>
+        <v>-1.3598</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0694</v>
+        <v>-1.1022</v>
       </c>
       <c r="P9" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.2487</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-2.2893</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4684</v>
+        <v>1.397</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.7778</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1188</v>
+        <v>0.6192</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1675</v>
+        <v>-1.1675</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5647</v>
+        <v>-1.2493</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1581</v>
+        <v>-1.7789</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4066</v>
+        <v>0.5296</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6255</v>
+        <v>-1.3762</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8401</v>
+        <v>-0.5051</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7854</v>
+        <v>-0.8711</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8364</v>
+        <v>-0.629</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5196</v>
+        <v>0.1727</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3167</v>
+        <v>-0.8017</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4619</v>
+        <v>-0.7472</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3598</v>
+        <v>-0.6778</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1022</v>
+        <v>-0.0694</v>
       </c>
       <c r="P10" t="n">
+        <v>-1.2487</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2.2893</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.0406</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.2081</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.2487</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4568</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.0202</v>
-      </c>
       <c r="T10" t="n">
-        <v>-0.7458</v>
+        <v>-0.0281</v>
       </c>
       <c r="U10" t="n">
-        <v>0.766</v>
+        <v>0.2362</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1675</v>
+        <v>1.1675</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7433</v>
+        <v>-2.6572</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0044</v>
+        <v>-3.1238</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2611</v>
+        <v>0.4666</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7049</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8136</v>
+        <v>0.2725</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8482</v>
+        <v>0.0324</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0346</v>
+        <v>0.2401</v>
       </c>
       <c r="V11" t="n">
         <v>2.6889</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.863300000000002</v>
+        <v>5.841800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.711799999999998</v>
+        <v>3.690500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1516</v>
+        <v>2.1513</v>
       </c>
       <c r="G12" t="n">
         <v>-6.9193</v>
@@ -1363,10 +1363,10 @@
         <v>-5.0006</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3293</v>
+        <v>4.329300000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>4.186400000000001</v>
+        <v>4.1864</v>
       </c>
       <c r="L12" t="n">
         <v>0.1427999999999998</v>
@@ -1390,13 +1390,13 @@
         <v>13.5277</v>
       </c>
       <c r="S12" t="n">
-        <v>8.836600000000002</v>
+        <v>9.815400000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>5.3557</v>
+        <v>6.3343</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4812</v>
+        <v>3.4811</v>
       </c>
       <c r="V12" t="n">
         <v>6.0677</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0917</v>
+        <v>5.2528</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0599</v>
+        <v>3.3814</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0318</v>
+        <v>1.8714</v>
       </c>
       <c r="G13" t="n">
         <v>5.9641</v>
@@ -1468,13 +1468,13 @@
         <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8724</v>
+        <v>-0.7113</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0967</v>
+        <v>-0.7753</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7756999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5796</v>
+        <v>4.9257</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6835</v>
+        <v>4.2192</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1038</v>
+        <v>0.7065</v>
       </c>
       <c r="G14" t="n">
         <v>5.6769</v>
@@ -1546,13 +1546,13 @@
         <v>2.7055</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.0754</v>
+        <v>-1.7294</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3577</v>
+        <v>-0.8219</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.7177</v>
+        <v>-0.9074</v>
       </c>
       <c r="V14" t="n">
         <v>0.3538</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9296</v>
+        <v>0.9344</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0279</v>
+        <v>0.2422</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.6922</v>
       </c>
       <c r="G15" t="n">
         <v>1.2909</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7131</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7705</v>
+        <v>-0.5562</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0575</v>
+        <v>-0.152</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5213</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4683</v>
+        <v>0.5754</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0292</v>
+        <v>0.078</v>
       </c>
       <c r="F16" t="n">
         <v>0.4974</v>
@@ -1702,10 +1702,10 @@
         <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0776</v>
+        <v>0.0295</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.261</v>
+        <v>-0.1538</v>
       </c>
       <c r="U16" t="n">
         <v>0.1833</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2972</v>
+        <v>-0.4528</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0399</v>
+        <v>0.8256</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3371</v>
+        <v>-1.2784</v>
       </c>
       <c r="G17" t="n">
         <v>0.4026</v>
@@ -1780,13 +1780,13 @@
         <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3647</v>
+        <v>-0.5203</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3882</v>
+        <v>0.1738</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7529</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1675</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9351</v>
+        <v>-0.574</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7942</v>
+        <v>-1.0085</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.141</v>
+        <v>0.4344</v>
       </c>
       <c r="G18" t="n">
         <v>1.2961</v>
@@ -1858,13 +1858,13 @@
         <v>2.4974</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5018</v>
+        <v>-1.1407</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4476</v>
+        <v>-0.6619</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0542</v>
+        <v>-0.4788</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9376</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2092</v>
+        <v>-1.5997</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1725</v>
+        <v>-2.3869</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9633</v>
+        <v>0.7872</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0794</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7026</v>
+        <v>0.3122</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3882</v>
+        <v>0.1738</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3145</v>
+        <v>0.1383</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.489</v>
+        <v>-1.7238</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0217</v>
+        <v>-0.4503</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4673</v>
+        <v>-1.2735</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7701</v>
@@ -2014,13 +2014,13 @@
         <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0509</v>
+        <v>-0.2857</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1272</v>
+        <v>-0.3014</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1781</v>
+        <v>0.0157</v>
       </c>
       <c r="V20" t="n">
         <v>0.1238</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7696</v>
+        <v>-1.7887</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7523</v>
+        <v>-0.8594000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0173</v>
+        <v>-0.9292</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5208</v>
@@ -2092,13 +2092,13 @@
         <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4756</v>
+        <v>-0.4947</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0033</v>
+        <v>-0.1105</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4723</v>
+        <v>-0.3842</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8137</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7939</v>
+        <v>-2.9788</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3025</v>
+        <v>-1.5168</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4914</v>
+        <v>-1.4621</v>
       </c>
       <c r="G22" t="n">
         <v>-2.071</v>
@@ -2170,13 +2170,13 @@
         <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7229</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2577</v>
+        <v>0.0434</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9806</v>
+        <v>-0.9512</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4383</v>
+        <v>-5.2905</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8902</v>
+        <v>-4.6759</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.548</v>
+        <v>-0.6146</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4401</v>
@@ -2248,13 +2248,13 @@
         <v>1.8731</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5372</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7053</v>
+        <v>-0.491</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0203</v>
+        <v>-0.0463</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1051</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.863099999999999</v>
+        <v>-2.719999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.151400000000001</v>
+        <v>-2.1514</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7117</v>
+        <v>-0.5687000000000002</v>
       </c>
       <c r="G24" t="n">
         <v>6.9194</v>
@@ -2326,13 +2326,13 @@
         <v>16.6494</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.8368</v>
+        <v>-6.6936</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.480799999999999</v>
+        <v>-3.481</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.3559</v>
+        <v>-3.2127</v>
       </c>
       <c r="V24" t="n">
         <v>-6.067600000000001</v>
